--- a/apptestingreport.xlsx
+++ b/apptestingreport.xlsx
@@ -20,13 +20,13 @@
     <t>Test Run Date:</t>
   </si>
   <si>
-    <t>2026-06-16</t>
+    <t>2026-06-17</t>
   </si>
   <si>
     <t>Test Run Time:</t>
   </si>
   <si>
-    <t>22:31:48</t>
+    <t>20:59:54</t>
   </si>
   <si>
     <t>OS / Platform:</t>
@@ -686,7 +686,7 @@
     <t>TC-API-010</t>
   </si>
   <si>
-    <t>Logout returned success response without active session.</t>
+    <t>Logout endpoint confirmed no active session (request aborted / no session cookie).</t>
   </si>
   <si>
     <t>TC-API-011</t>
@@ -3107,7 +3107,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="7">
-        <v>350.44</v>
+        <v>352.17</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3362,7 +3362,7 @@
         <v>42</v>
       </c>
       <c r="F2" s="17">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3382,7 +3382,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="17">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3402,7 +3402,7 @@
         <v>42</v>
       </c>
       <c r="F4" s="17">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,7 +3422,7 @@
         <v>42</v>
       </c>
       <c r="F5" s="17">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3442,7 +3442,7 @@
         <v>42</v>
       </c>
       <c r="F6" s="17">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3462,7 +3462,7 @@
         <v>42</v>
       </c>
       <c r="F7" s="17">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3482,7 +3482,7 @@
         <v>42</v>
       </c>
       <c r="F8" s="17">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3502,7 +3502,7 @@
         <v>42</v>
       </c>
       <c r="F9" s="17">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3522,7 +3522,7 @@
         <v>42</v>
       </c>
       <c r="F10" s="17">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3542,7 +3542,7 @@
         <v>42</v>
       </c>
       <c r="F11" s="17">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3562,7 +3562,7 @@
         <v>42</v>
       </c>
       <c r="F12" s="17">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3582,7 +3582,7 @@
         <v>42</v>
       </c>
       <c r="F13" s="17">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3602,7 +3602,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="17">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3622,7 +3622,7 @@
         <v>42</v>
       </c>
       <c r="F15" s="17">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3642,7 +3642,7 @@
         <v>42</v>
       </c>
       <c r="F16" s="17">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3662,7 +3662,7 @@
         <v>42</v>
       </c>
       <c r="F17" s="17">
-        <v>0.44</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3682,7 +3682,7 @@
         <v>42</v>
       </c>
       <c r="F18" s="17">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3702,7 +3702,7 @@
         <v>42</v>
       </c>
       <c r="F19" s="17">
-        <v>0.48</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3722,7 +3722,7 @@
         <v>42</v>
       </c>
       <c r="F20" s="17">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3742,7 +3742,7 @@
         <v>42</v>
       </c>
       <c r="F21" s="17">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3762,7 +3762,7 @@
         <v>42</v>
       </c>
       <c r="F22" s="17">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3782,7 +3782,7 @@
         <v>42</v>
       </c>
       <c r="F23" s="17">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3802,7 +3802,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="17">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3822,7 +3822,7 @@
         <v>42</v>
       </c>
       <c r="F25" s="17">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3842,7 +3842,7 @@
         <v>42</v>
       </c>
       <c r="F26" s="17">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3862,7 +3862,7 @@
         <v>42</v>
       </c>
       <c r="F27" s="17">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3882,7 +3882,7 @@
         <v>42</v>
       </c>
       <c r="F28" s="17">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3902,7 +3902,7 @@
         <v>42</v>
       </c>
       <c r="F29" s="17">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3922,7 +3922,7 @@
         <v>42</v>
       </c>
       <c r="F30" s="17">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3942,7 +3942,7 @@
         <v>42</v>
       </c>
       <c r="F31" s="17">
-        <v>0.36</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3962,7 +3962,7 @@
         <v>42</v>
       </c>
       <c r="F32" s="17">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -3982,7 +3982,7 @@
         <v>42</v>
       </c>
       <c r="F33" s="17">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4002,7 +4002,7 @@
         <v>42</v>
       </c>
       <c r="F34" s="17">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
         <v>42</v>
       </c>
       <c r="F35" s="17">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4042,7 +4042,7 @@
         <v>42</v>
       </c>
       <c r="F36" s="17">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4062,7 +4062,7 @@
         <v>42</v>
       </c>
       <c r="F37" s="17">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4082,7 +4082,7 @@
         <v>42</v>
       </c>
       <c r="F38" s="17">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4102,7 +4102,7 @@
         <v>42</v>
       </c>
       <c r="F39" s="17">
-        <v>0.48</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4122,7 +4122,7 @@
         <v>42</v>
       </c>
       <c r="F40" s="17">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4142,7 +4142,7 @@
         <v>42</v>
       </c>
       <c r="F41" s="17">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4162,7 +4162,7 @@
         <v>42</v>
       </c>
       <c r="F42" s="17">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,7 +4182,7 @@
         <v>42</v>
       </c>
       <c r="F43" s="17">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4202,7 +4202,7 @@
         <v>42</v>
       </c>
       <c r="F44" s="17">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4222,7 +4222,7 @@
         <v>42</v>
       </c>
       <c r="F45" s="17">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4242,7 +4242,7 @@
         <v>42</v>
       </c>
       <c r="F46" s="17">
-        <v>0.19</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4262,7 +4262,7 @@
         <v>42</v>
       </c>
       <c r="F47" s="17">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4282,7 +4282,7 @@
         <v>42</v>
       </c>
       <c r="F48" s="17">
-        <v>0.48</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4302,7 +4302,7 @@
         <v>42</v>
       </c>
       <c r="F49" s="17">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,7 +4322,7 @@
         <v>42</v>
       </c>
       <c r="F50" s="17">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4342,7 +4342,7 @@
         <v>42</v>
       </c>
       <c r="F51" s="17">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4362,7 +4362,7 @@
         <v>42</v>
       </c>
       <c r="F52" s="17">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4382,7 +4382,7 @@
         <v>42</v>
       </c>
       <c r="F53" s="17">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4402,7 +4402,7 @@
         <v>42</v>
       </c>
       <c r="F54" s="17">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4422,7 +4422,7 @@
         <v>42</v>
       </c>
       <c r="F55" s="17">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4442,7 +4442,7 @@
         <v>42</v>
       </c>
       <c r="F56" s="17">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4462,7 +4462,7 @@
         <v>42</v>
       </c>
       <c r="F57" s="17">
-        <v>0.39</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4482,7 +4482,7 @@
         <v>42</v>
       </c>
       <c r="F58" s="17">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4502,7 +4502,7 @@
         <v>42</v>
       </c>
       <c r="F59" s="17">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4522,7 +4522,7 @@
         <v>42</v>
       </c>
       <c r="F60" s="17">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4542,7 +4542,7 @@
         <v>42</v>
       </c>
       <c r="F61" s="17">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4562,7 +4562,7 @@
         <v>42</v>
       </c>
       <c r="F62" s="17">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4582,7 +4582,7 @@
         <v>42</v>
       </c>
       <c r="F63" s="17">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4602,7 +4602,7 @@
         <v>42</v>
       </c>
       <c r="F64" s="17">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4622,7 +4622,7 @@
         <v>42</v>
       </c>
       <c r="F65" s="17">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4642,7 +4642,7 @@
         <v>42</v>
       </c>
       <c r="F66" s="17">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4662,7 +4662,7 @@
         <v>42</v>
       </c>
       <c r="F67" s="17">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4682,7 +4682,7 @@
         <v>42</v>
       </c>
       <c r="F68" s="17">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4702,7 +4702,7 @@
         <v>42</v>
       </c>
       <c r="F69" s="17">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,7 +4722,7 @@
         <v>42</v>
       </c>
       <c r="F70" s="17">
-        <v>0.43</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4742,7 +4742,7 @@
         <v>42</v>
       </c>
       <c r="F71" s="17">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4762,7 +4762,7 @@
         <v>42</v>
       </c>
       <c r="F72" s="17">
-        <v>0.46</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4782,7 +4782,7 @@
         <v>42</v>
       </c>
       <c r="F73" s="17">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4802,7 +4802,7 @@
         <v>42</v>
       </c>
       <c r="F74" s="17">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4822,7 +4822,7 @@
         <v>42</v>
       </c>
       <c r="F75" s="17">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4842,7 +4842,7 @@
         <v>42</v>
       </c>
       <c r="F76" s="17">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4862,7 +4862,7 @@
         <v>42</v>
       </c>
       <c r="F77" s="17">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4882,7 +4882,7 @@
         <v>42</v>
       </c>
       <c r="F78" s="17">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4902,7 +4902,7 @@
         <v>42</v>
       </c>
       <c r="F79" s="17">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4922,7 +4922,7 @@
         <v>42</v>
       </c>
       <c r="F80" s="17">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4942,7 +4942,7 @@
         <v>42</v>
       </c>
       <c r="F81" s="17">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4962,7 +4962,7 @@
         <v>42</v>
       </c>
       <c r="F82" s="17">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4982,7 +4982,7 @@
         <v>42</v>
       </c>
       <c r="F83" s="17">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5002,7 +5002,7 @@
         <v>42</v>
       </c>
       <c r="F84" s="17">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5022,7 +5022,7 @@
         <v>42</v>
       </c>
       <c r="F85" s="17">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5042,7 +5042,7 @@
         <v>42</v>
       </c>
       <c r="F86" s="17">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5062,7 +5062,7 @@
         <v>42</v>
       </c>
       <c r="F87" s="17">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5082,7 +5082,7 @@
         <v>42</v>
       </c>
       <c r="F88" s="17">
-        <v>0.36</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>42</v>
       </c>
       <c r="F89" s="17">
-        <v>0.26</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5122,7 +5122,7 @@
         <v>42</v>
       </c>
       <c r="F90" s="17">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5142,7 +5142,7 @@
         <v>42</v>
       </c>
       <c r="F91" s="17">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5162,7 +5162,7 @@
         <v>42</v>
       </c>
       <c r="F92" s="17">
-        <v>0.42</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5182,7 +5182,7 @@
         <v>42</v>
       </c>
       <c r="F93" s="17">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5202,7 +5202,7 @@
         <v>42</v>
       </c>
       <c r="F94" s="17">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5222,7 +5222,7 @@
         <v>42</v>
       </c>
       <c r="F95" s="17">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5242,7 +5242,7 @@
         <v>42</v>
       </c>
       <c r="F96" s="17">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5262,7 +5262,7 @@
         <v>42</v>
       </c>
       <c r="F97" s="17">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5282,7 +5282,7 @@
         <v>42</v>
       </c>
       <c r="F98" s="17">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5302,7 +5302,7 @@
         <v>42</v>
       </c>
       <c r="F99" s="17">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5322,7 +5322,7 @@
         <v>42</v>
       </c>
       <c r="F100" s="17">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5342,7 +5342,7 @@
         <v>42</v>
       </c>
       <c r="F101" s="17">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5362,7 +5362,7 @@
         <v>42</v>
       </c>
       <c r="F102" s="17">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5382,7 +5382,7 @@
         <v>42</v>
       </c>
       <c r="F103" s="17">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5402,7 +5402,7 @@
         <v>42</v>
       </c>
       <c r="F104" s="17">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5422,7 +5422,7 @@
         <v>42</v>
       </c>
       <c r="F105" s="17">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5442,7 +5442,7 @@
         <v>42</v>
       </c>
       <c r="F106" s="17">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5462,7 +5462,7 @@
         <v>42</v>
       </c>
       <c r="F107" s="17">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5502,7 +5502,7 @@
         <v>42</v>
       </c>
       <c r="F109" s="17">
-        <v>0.45</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5522,7 +5522,7 @@
         <v>42</v>
       </c>
       <c r="F110" s="17">
-        <v>0.48</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5542,7 +5542,7 @@
         <v>42</v>
       </c>
       <c r="F111" s="17">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5562,7 +5562,7 @@
         <v>42</v>
       </c>
       <c r="F112" s="17">
-        <v>0.4</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5582,7 +5582,7 @@
         <v>42</v>
       </c>
       <c r="F113" s="17">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5602,7 +5602,7 @@
         <v>42</v>
       </c>
       <c r="F114" s="17">
-        <v>0.24</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5622,7 +5622,7 @@
         <v>42</v>
       </c>
       <c r="F115" s="17">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5642,7 +5642,7 @@
         <v>42</v>
       </c>
       <c r="F116" s="17">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5662,7 +5662,7 @@
         <v>42</v>
       </c>
       <c r="F117" s="17">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5682,7 +5682,7 @@
         <v>42</v>
       </c>
       <c r="F118" s="17">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5702,7 +5702,7 @@
         <v>42</v>
       </c>
       <c r="F119" s="17">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5722,7 +5722,7 @@
         <v>42</v>
       </c>
       <c r="F120" s="17">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5742,7 +5742,7 @@
         <v>42</v>
       </c>
       <c r="F121" s="17">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5762,7 +5762,7 @@
         <v>42</v>
       </c>
       <c r="F122" s="17">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5782,7 +5782,7 @@
         <v>42</v>
       </c>
       <c r="F123" s="17">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5822,7 +5822,7 @@
         <v>42</v>
       </c>
       <c r="F125" s="17">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5842,7 +5842,7 @@
         <v>42</v>
       </c>
       <c r="F126" s="17">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5862,7 +5862,7 @@
         <v>42</v>
       </c>
       <c r="F127" s="17">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5882,7 +5882,7 @@
         <v>42</v>
       </c>
       <c r="F128" s="17">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5902,7 +5902,7 @@
         <v>42</v>
       </c>
       <c r="F129" s="17">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5922,7 +5922,7 @@
         <v>42</v>
       </c>
       <c r="F130" s="17">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5942,7 +5942,7 @@
         <v>42</v>
       </c>
       <c r="F131" s="17">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5962,7 +5962,7 @@
         <v>42</v>
       </c>
       <c r="F132" s="17">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5982,7 +5982,7 @@
         <v>42</v>
       </c>
       <c r="F133" s="17">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6002,7 +6002,7 @@
         <v>42</v>
       </c>
       <c r="F134" s="17">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6062,7 +6062,7 @@
         <v>42</v>
       </c>
       <c r="F137" s="17">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6082,7 +6082,7 @@
         <v>42</v>
       </c>
       <c r="F138" s="17">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6102,7 +6102,7 @@
         <v>42</v>
       </c>
       <c r="F139" s="17">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6122,7 +6122,7 @@
         <v>42</v>
       </c>
       <c r="F140" s="17">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6142,7 +6142,7 @@
         <v>42</v>
       </c>
       <c r="F141" s="17">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6162,7 +6162,7 @@
         <v>42</v>
       </c>
       <c r="F142" s="17">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6182,7 +6182,7 @@
         <v>42</v>
       </c>
       <c r="F143" s="17">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6202,7 +6202,7 @@
         <v>42</v>
       </c>
       <c r="F144" s="17">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6222,7 +6222,7 @@
         <v>42</v>
       </c>
       <c r="F145" s="17">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6242,7 +6242,7 @@
         <v>42</v>
       </c>
       <c r="F146" s="17">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6262,7 +6262,7 @@
         <v>42</v>
       </c>
       <c r="F147" s="17">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6282,7 +6282,7 @@
         <v>42</v>
       </c>
       <c r="F148" s="17">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6302,7 +6302,7 @@
         <v>42</v>
       </c>
       <c r="F149" s="17">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6322,7 +6322,7 @@
         <v>42</v>
       </c>
       <c r="F150" s="17">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6362,7 +6362,7 @@
         <v>42</v>
       </c>
       <c r="F152" s="17">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6382,7 +6382,7 @@
         <v>42</v>
       </c>
       <c r="F153" s="17">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6402,7 +6402,7 @@
         <v>42</v>
       </c>
       <c r="F154" s="17">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6422,7 +6422,7 @@
         <v>42</v>
       </c>
       <c r="F155" s="17">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6442,7 +6442,7 @@
         <v>42</v>
       </c>
       <c r="F156" s="17">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6502,7 +6502,7 @@
         <v>42</v>
       </c>
       <c r="F159" s="17">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6522,7 +6522,7 @@
         <v>42</v>
       </c>
       <c r="F160" s="17">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6542,7 +6542,7 @@
         <v>42</v>
       </c>
       <c r="F161" s="17">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6562,7 +6562,7 @@
         <v>42</v>
       </c>
       <c r="F162" s="17">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6582,7 +6582,7 @@
         <v>42</v>
       </c>
       <c r="F163" s="17">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6602,7 +6602,7 @@
         <v>42</v>
       </c>
       <c r="F164" s="17">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6622,7 +6622,7 @@
         <v>42</v>
       </c>
       <c r="F165" s="17">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6642,7 +6642,7 @@
         <v>42</v>
       </c>
       <c r="F166" s="17">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6662,7 +6662,7 @@
         <v>42</v>
       </c>
       <c r="F167" s="17">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6682,7 +6682,7 @@
         <v>42</v>
       </c>
       <c r="F168" s="17">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6742,7 +6742,7 @@
         <v>42</v>
       </c>
       <c r="F171" s="17">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6762,7 +6762,7 @@
         <v>42</v>
       </c>
       <c r="F172" s="17">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6782,7 +6782,7 @@
         <v>42</v>
       </c>
       <c r="F173" s="17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6802,7 +6802,7 @@
         <v>42</v>
       </c>
       <c r="F174" s="17">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6822,7 +6822,7 @@
         <v>42</v>
       </c>
       <c r="F175" s="17">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6842,7 +6842,7 @@
         <v>42</v>
       </c>
       <c r="F176" s="17">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6882,7 +6882,7 @@
         <v>42</v>
       </c>
       <c r="F178" s="17">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6902,7 +6902,7 @@
         <v>42</v>
       </c>
       <c r="F179" s="17">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6922,7 +6922,7 @@
         <v>42</v>
       </c>
       <c r="F180" s="17">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6942,7 +6942,7 @@
         <v>42</v>
       </c>
       <c r="F181" s="17">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6962,7 +6962,7 @@
         <v>42</v>
       </c>
       <c r="F182" s="17">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6982,7 +6982,7 @@
         <v>42</v>
       </c>
       <c r="F183" s="17">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7002,7 +7002,7 @@
         <v>42</v>
       </c>
       <c r="F184" s="17">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7022,7 +7022,7 @@
         <v>42</v>
       </c>
       <c r="F185" s="17">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7042,7 +7042,7 @@
         <v>42</v>
       </c>
       <c r="F186" s="17">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7062,7 +7062,7 @@
         <v>42</v>
       </c>
       <c r="F187" s="17">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7082,7 +7082,7 @@
         <v>42</v>
       </c>
       <c r="F188" s="17">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7102,7 +7102,7 @@
         <v>42</v>
       </c>
       <c r="F189" s="17">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7122,7 +7122,7 @@
         <v>42</v>
       </c>
       <c r="F190" s="17">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7142,7 +7142,7 @@
         <v>42</v>
       </c>
       <c r="F191" s="17">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7162,7 +7162,7 @@
         <v>42</v>
       </c>
       <c r="F192" s="17">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7182,7 +7182,7 @@
         <v>42</v>
       </c>
       <c r="F193" s="17">
-        <v>0.07</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7222,7 +7222,7 @@
         <v>42</v>
       </c>
       <c r="F195" s="17">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7242,7 +7242,7 @@
         <v>42</v>
       </c>
       <c r="F196" s="17">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7262,7 +7262,7 @@
         <v>42</v>
       </c>
       <c r="F197" s="17">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7282,7 +7282,7 @@
         <v>42</v>
       </c>
       <c r="F198" s="17">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7322,7 +7322,7 @@
         <v>42</v>
       </c>
       <c r="F200" s="17">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7342,7 +7342,7 @@
         <v>42</v>
       </c>
       <c r="F201" s="17">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7362,7 +7362,7 @@
         <v>42</v>
       </c>
       <c r="F202" s="17">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7382,7 +7382,7 @@
         <v>42</v>
       </c>
       <c r="F203" s="17">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7402,7 +7402,7 @@
         <v>42</v>
       </c>
       <c r="F204" s="17">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7422,7 +7422,7 @@
         <v>42</v>
       </c>
       <c r="F205" s="17">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7442,7 +7442,7 @@
         <v>42</v>
       </c>
       <c r="F206" s="17">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7462,7 +7462,7 @@
         <v>42</v>
       </c>
       <c r="F207" s="17">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7482,7 +7482,7 @@
         <v>42</v>
       </c>
       <c r="F208" s="17">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7502,7 +7502,7 @@
         <v>42</v>
       </c>
       <c r="F209" s="17">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7542,7 +7542,7 @@
         <v>42</v>
       </c>
       <c r="F211" s="17">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7562,7 +7562,7 @@
         <v>42</v>
       </c>
       <c r="F212" s="17">
-        <v>0.11</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7582,7 +7582,7 @@
         <v>42</v>
       </c>
       <c r="F213" s="17">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7602,7 +7602,7 @@
         <v>42</v>
       </c>
       <c r="F214" s="17">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7622,7 +7622,7 @@
         <v>42</v>
       </c>
       <c r="F215" s="17">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7642,7 +7642,7 @@
         <v>42</v>
       </c>
       <c r="F216" s="17">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7662,7 +7662,7 @@
         <v>42</v>
       </c>
       <c r="F217" s="17">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="218" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7682,7 +7682,7 @@
         <v>42</v>
       </c>
       <c r="F218" s="17">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="219" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7722,7 +7722,7 @@
         <v>42</v>
       </c>
       <c r="F220" s="17">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7742,7 +7742,7 @@
         <v>42</v>
       </c>
       <c r="F221" s="17">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="222" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7762,7 +7762,7 @@
         <v>42</v>
       </c>
       <c r="F222" s="17">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7782,7 +7782,7 @@
         <v>42</v>
       </c>
       <c r="F223" s="17">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="224" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7802,7 +7802,7 @@
         <v>42</v>
       </c>
       <c r="F224" s="17">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="225" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7822,7 +7822,7 @@
         <v>42</v>
       </c>
       <c r="F225" s="17">
-        <v>0.07</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="226" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7862,7 +7862,7 @@
         <v>42</v>
       </c>
       <c r="F227" s="17">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="228" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7882,7 +7882,7 @@
         <v>42</v>
       </c>
       <c r="F228" s="17">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="229" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7902,7 +7902,7 @@
         <v>42</v>
       </c>
       <c r="F229" s="17">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="230" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7922,7 +7922,7 @@
         <v>42</v>
       </c>
       <c r="F230" s="17">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="231" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7942,7 +7942,7 @@
         <v>42</v>
       </c>
       <c r="F231" s="17">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7962,7 +7962,7 @@
         <v>42</v>
       </c>
       <c r="F232" s="17">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="233" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7982,7 +7982,7 @@
         <v>42</v>
       </c>
       <c r="F233" s="17">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="234" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8002,7 +8002,7 @@
         <v>42</v>
       </c>
       <c r="F234" s="17">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="235" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8022,7 +8022,7 @@
         <v>42</v>
       </c>
       <c r="F235" s="17">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8042,7 +8042,7 @@
         <v>42</v>
       </c>
       <c r="F236" s="17">
-        <v>0.42</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="237" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8062,7 +8062,7 @@
         <v>42</v>
       </c>
       <c r="F237" s="17">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8082,7 +8082,7 @@
         <v>42</v>
       </c>
       <c r="F238" s="17">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="239" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8102,7 +8102,7 @@
         <v>42</v>
       </c>
       <c r="F239" s="17">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="240" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8122,7 +8122,7 @@
         <v>42</v>
       </c>
       <c r="F240" s="17">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="241" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8142,7 +8142,7 @@
         <v>42</v>
       </c>
       <c r="F241" s="17">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="242" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8162,7 +8162,7 @@
         <v>42</v>
       </c>
       <c r="F242" s="17">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8182,7 +8182,7 @@
         <v>42</v>
       </c>
       <c r="F243" s="17">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="244" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8202,7 +8202,7 @@
         <v>42</v>
       </c>
       <c r="F244" s="17">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="245" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8222,7 +8222,7 @@
         <v>42</v>
       </c>
       <c r="F245" s="17">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="246" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8242,7 +8242,7 @@
         <v>42</v>
       </c>
       <c r="F246" s="17">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8262,7 +8262,7 @@
         <v>42</v>
       </c>
       <c r="F247" s="17">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="248" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8282,7 +8282,7 @@
         <v>42</v>
       </c>
       <c r="F248" s="17">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="249" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8302,7 +8302,7 @@
         <v>42</v>
       </c>
       <c r="F249" s="17">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="250" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8322,7 +8322,7 @@
         <v>42</v>
       </c>
       <c r="F250" s="17">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="251" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8342,7 +8342,7 @@
         <v>42</v>
       </c>
       <c r="F251" s="17">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="252" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8362,7 +8362,7 @@
         <v>42</v>
       </c>
       <c r="F252" s="17">
-        <v>0.31</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="253" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8382,7 +8382,7 @@
         <v>42</v>
       </c>
       <c r="F253" s="17">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="254" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8402,7 +8402,7 @@
         <v>42</v>
       </c>
       <c r="F254" s="17">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="255" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8422,7 +8422,7 @@
         <v>42</v>
       </c>
       <c r="F255" s="17">
-        <v>0.5</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="256" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8442,7 +8442,7 @@
         <v>42</v>
       </c>
       <c r="F256" s="17">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="257" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8462,7 +8462,7 @@
         <v>42</v>
       </c>
       <c r="F257" s="17">
-        <v>0.14</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="258" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8482,7 +8482,7 @@
         <v>42</v>
       </c>
       <c r="F258" s="17">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="259" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8502,7 +8502,7 @@
         <v>42</v>
       </c>
       <c r="F259" s="17">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="260" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8522,7 +8522,7 @@
         <v>42</v>
       </c>
       <c r="F260" s="17">
-        <v>0.47</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="261" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8542,7 +8542,7 @@
         <v>42</v>
       </c>
       <c r="F261" s="17">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="262" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8562,7 +8562,7 @@
         <v>42</v>
       </c>
       <c r="F262" s="17">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="263" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8582,7 +8582,7 @@
         <v>42</v>
       </c>
       <c r="F263" s="17">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="264" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8602,7 +8602,7 @@
         <v>42</v>
       </c>
       <c r="F264" s="17">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="265" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8622,7 +8622,7 @@
         <v>42</v>
       </c>
       <c r="F265" s="17">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="266" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8642,7 +8642,7 @@
         <v>42</v>
       </c>
       <c r="F266" s="17">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="267" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8662,7 +8662,7 @@
         <v>42</v>
       </c>
       <c r="F267" s="17">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="268" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8682,7 +8682,7 @@
         <v>42</v>
       </c>
       <c r="F268" s="17">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="269" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8702,7 +8702,7 @@
         <v>42</v>
       </c>
       <c r="F269" s="17">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="270" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8722,7 +8722,7 @@
         <v>42</v>
       </c>
       <c r="F270" s="17">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="271" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8762,7 +8762,7 @@
         <v>42</v>
       </c>
       <c r="F272" s="17">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="273" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8782,7 +8782,7 @@
         <v>42</v>
       </c>
       <c r="F273" s="17">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="274" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8802,7 +8802,7 @@
         <v>42</v>
       </c>
       <c r="F274" s="17">
-        <v>0.18</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="275" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8822,7 +8822,7 @@
         <v>42</v>
       </c>
       <c r="F275" s="17">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="276" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8842,7 +8842,7 @@
         <v>42</v>
       </c>
       <c r="F276" s="17">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="277" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8862,7 +8862,7 @@
         <v>42</v>
       </c>
       <c r="F277" s="17">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="278" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8882,7 +8882,7 @@
         <v>42</v>
       </c>
       <c r="F278" s="17">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="279" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8902,7 +8902,7 @@
         <v>42</v>
       </c>
       <c r="F279" s="17">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="280" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8922,7 +8922,7 @@
         <v>42</v>
       </c>
       <c r="F280" s="17">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="281" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8942,7 +8942,7 @@
         <v>42</v>
       </c>
       <c r="F281" s="17">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="282" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8962,7 +8962,7 @@
         <v>42</v>
       </c>
       <c r="F282" s="17">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="283" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8982,7 +8982,7 @@
         <v>42</v>
       </c>
       <c r="F283" s="17">
-        <v>0.21</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="284" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9002,7 +9002,7 @@
         <v>42</v>
       </c>
       <c r="F284" s="17">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="285" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9022,7 +9022,7 @@
         <v>42</v>
       </c>
       <c r="F285" s="17">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="286" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9042,7 +9042,7 @@
         <v>42</v>
       </c>
       <c r="F286" s="17">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="287" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9062,7 +9062,7 @@
         <v>42</v>
       </c>
       <c r="F287" s="17">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="288" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9082,7 +9082,7 @@
         <v>42</v>
       </c>
       <c r="F288" s="17">
-        <v>0.35</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="289" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9102,7 +9102,7 @@
         <v>42</v>
       </c>
       <c r="F289" s="17">
-        <v>0.42</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="290" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9122,7 +9122,7 @@
         <v>42</v>
       </c>
       <c r="F290" s="17">
-        <v>0.39</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="291" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9142,7 +9142,7 @@
         <v>42</v>
       </c>
       <c r="F291" s="17">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="292" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9162,7 +9162,7 @@
         <v>42</v>
       </c>
       <c r="F292" s="17">
-        <v>0.29</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="293" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9182,7 +9182,7 @@
         <v>42</v>
       </c>
       <c r="F293" s="17">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="294" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9202,7 +9202,7 @@
         <v>42</v>
       </c>
       <c r="F294" s="17">
-        <v>0.33</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="295" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9222,7 +9222,7 @@
         <v>42</v>
       </c>
       <c r="F295" s="17">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="296" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9242,7 +9242,7 @@
         <v>42</v>
       </c>
       <c r="F296" s="17">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="297" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9262,7 +9262,7 @@
         <v>42</v>
       </c>
       <c r="F297" s="17">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="298" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9282,7 +9282,7 @@
         <v>42</v>
       </c>
       <c r="F298" s="17">
-        <v>0.31</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="299" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9302,7 +9302,7 @@
         <v>42</v>
       </c>
       <c r="F299" s="17">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="300" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9322,7 +9322,7 @@
         <v>42</v>
       </c>
       <c r="F300" s="17">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="301" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9342,7 +9342,7 @@
         <v>42</v>
       </c>
       <c r="F301" s="17">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="302" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9362,7 +9362,7 @@
         <v>42</v>
       </c>
       <c r="F302" s="17">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="303" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9382,7 +9382,7 @@
         <v>42</v>
       </c>
       <c r="F303" s="17">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="304" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9402,7 +9402,7 @@
         <v>42</v>
       </c>
       <c r="F304" s="17">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="305" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9422,7 +9422,7 @@
         <v>42</v>
       </c>
       <c r="F305" s="17">
-        <v>0.49</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="306" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9442,7 +9442,7 @@
         <v>42</v>
       </c>
       <c r="F306" s="17">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="307" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9462,7 +9462,7 @@
         <v>42</v>
       </c>
       <c r="F307" s="17">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="308" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9482,7 +9482,7 @@
         <v>42</v>
       </c>
       <c r="F308" s="17">
-        <v>0.48</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="309" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9502,7 +9502,7 @@
         <v>42</v>
       </c>
       <c r="F309" s="17">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="310" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9522,7 +9522,7 @@
         <v>42</v>
       </c>
       <c r="F310" s="17">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="311" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9542,7 +9542,7 @@
         <v>42</v>
       </c>
       <c r="F311" s="17">
-        <v>0.43</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="312" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9562,7 +9562,7 @@
         <v>42</v>
       </c>
       <c r="F312" s="17">
-        <v>0.43</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="313" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9582,7 +9582,7 @@
         <v>42</v>
       </c>
       <c r="F313" s="17">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="314" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9602,7 +9602,7 @@
         <v>42</v>
       </c>
       <c r="F314" s="17">
-        <v>0.49</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="315" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9622,7 +9622,7 @@
         <v>42</v>
       </c>
       <c r="F315" s="17">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="316" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9642,7 +9642,7 @@
         <v>42</v>
       </c>
       <c r="F316" s="17">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="317" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9662,7 +9662,7 @@
         <v>42</v>
       </c>
       <c r="F317" s="17">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="318" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9682,7 +9682,7 @@
         <v>42</v>
       </c>
       <c r="F318" s="17">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="319" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9702,7 +9702,7 @@
         <v>42</v>
       </c>
       <c r="F319" s="17">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="320" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9722,7 +9722,7 @@
         <v>42</v>
       </c>
       <c r="F320" s="17">
-        <v>0.17</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="321" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9742,7 +9742,7 @@
         <v>42</v>
       </c>
       <c r="F321" s="17">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="322" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9762,7 +9762,7 @@
         <v>42</v>
       </c>
       <c r="F322" s="17">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="323" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9782,7 +9782,7 @@
         <v>42</v>
       </c>
       <c r="F323" s="17">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="324" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9802,7 +9802,7 @@
         <v>42</v>
       </c>
       <c r="F324" s="17">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="325" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9822,7 +9822,7 @@
         <v>42</v>
       </c>
       <c r="F325" s="17">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="326" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9842,7 +9842,7 @@
         <v>42</v>
       </c>
       <c r="F326" s="17">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="327" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9862,7 +9862,7 @@
         <v>42</v>
       </c>
       <c r="F327" s="17">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="328" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9882,7 +9882,7 @@
         <v>42</v>
       </c>
       <c r="F328" s="17">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="329" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9902,7 +9902,7 @@
         <v>42</v>
       </c>
       <c r="F329" s="17">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="330" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9922,7 +9922,7 @@
         <v>42</v>
       </c>
       <c r="F330" s="17">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="331" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9942,7 +9942,7 @@
         <v>42</v>
       </c>
       <c r="F331" s="17">
-        <v>0.32</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="332" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9962,7 +9962,7 @@
         <v>42</v>
       </c>
       <c r="F332" s="17">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="333" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -9982,7 +9982,7 @@
         <v>42</v>
       </c>
       <c r="F333" s="17">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="334" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10002,7 +10002,7 @@
         <v>42</v>
       </c>
       <c r="F334" s="17">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="335" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10022,7 +10022,7 @@
         <v>42</v>
       </c>
       <c r="F335" s="17">
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="336" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10042,7 +10042,7 @@
         <v>42</v>
       </c>
       <c r="F336" s="17">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="337" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10062,7 +10062,7 @@
         <v>42</v>
       </c>
       <c r="F337" s="17">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="338" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10082,7 +10082,7 @@
         <v>42</v>
       </c>
       <c r="F338" s="17">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="339" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10102,7 +10102,7 @@
         <v>42</v>
       </c>
       <c r="F339" s="17">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="340" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10122,7 +10122,7 @@
         <v>42</v>
       </c>
       <c r="F340" s="17">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="341" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10142,7 +10142,7 @@
         <v>42</v>
       </c>
       <c r="F341" s="17">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="342" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
